--- a/test-output-result.xlsx
+++ b/test-output-result.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="67">
   <si>
     <t>单号</t>
   </si>
@@ -158,6 +158,30 @@
     <t>53 Maple Ave</t>
   </si>
   <si>
+    <t>4444 Test Lane</t>
+  </si>
+  <si>
+    <t>材料1</t>
+  </si>
+  <si>
+    <t>材料2</t>
+  </si>
+  <si>
+    <t>材料3</t>
+  </si>
+  <si>
+    <t>2月</t>
+  </si>
+  <si>
+    <t>材料4</t>
+  </si>
+  <si>
+    <t>3月</t>
+  </si>
+  <si>
+    <t>Chris材料</t>
+  </si>
+  <si>
     <t>9000 Ash Grove Crescent</t>
   </si>
   <si>
@@ -171,9 +195,6 @@
   </si>
   <si>
     <t>4月上</t>
-  </si>
-  <si>
-    <t>Chris材料</t>
   </si>
   <si>
     <t>Chris</t>
@@ -571,7 +592,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M142"/>
+  <dimension ref="A1:M129"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -1756,144 +1777,157 @@
         <v>10</v>
       </c>
     </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C121" t="s">
-        <v>2</v>
+        <v>47</v>
+      </c>
+      <c r="D121" t="s">
+        <v>12</v>
+      </c>
+      <c r="E121" t="s">
+        <v>13</v>
+      </c>
+      <c r="F121">
+        <v>10</v>
+      </c>
+      <c r="G121">
+        <v>14</v>
       </c>
       <c r="H121">
         <f>F121*G121</f>
       </c>
-    </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A122" t="s">
-        <v>22</v>
+      <c r="K121">
+        <v>100</v>
+      </c>
+      <c r="L121" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="122" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C122" t="s">
+        <v>47</v>
+      </c>
+      <c r="D122" t="s">
+        <v>21</v>
+      </c>
+      <c r="E122" t="s">
+        <v>23</v>
+      </c>
+      <c r="F122">
+        <v>5</v>
+      </c>
+      <c r="G122">
+        <v>13</v>
       </c>
       <c r="H122">
         <f>F122*G122</f>
       </c>
-    </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="K122">
+        <v>200</v>
+      </c>
+      <c r="L122" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="123" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>26</v>
+        <v>22</v>
+      </c>
+      <c r="B123">
+        <v>1000</v>
       </c>
       <c r="H123">
         <f>F123*G123</f>
       </c>
-    </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="K123">
+        <v>300</v>
+      </c>
+      <c r="L123" t="s">
+        <v>24</v>
+      </c>
+      <c r="M123" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="124" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H124">
         <f>F124*G124</f>
       </c>
-    </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="K124">
+        <v>400</v>
+      </c>
+      <c r="L124" t="s">
+        <v>50</v>
+      </c>
+      <c r="M124" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="125" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>28</v>
+      </c>
       <c r="H125">
         <f>F125*G125</f>
       </c>
-    </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="K125">
+        <v>500</v>
+      </c>
+      <c r="L125" t="s">
+        <v>52</v>
+      </c>
+      <c r="M125" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="126" spans="8:13" x14ac:dyDescent="0.25">
       <c r="H126">
         <f>F126*G126</f>
       </c>
-    </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="K126">
+        <v>600</v>
+      </c>
+      <c r="L126" t="s">
+        <v>54</v>
+      </c>
+      <c r="M126" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="127" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>29</v>
+      </c>
+      <c r="B127">
+        <f>SUM(H127:K127)</f>
+      </c>
       <c r="H127">
-        <f>F127*G127</f>
+        <f>SUM(H121:H126)</f>
+      </c>
+      <c r="I127">
+        <f>SUM(I121:I126)</f>
+      </c>
+      <c r="K127">
+        <f>SUM(K121:K126)</f>
       </c>
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="H128">
-        <f>F128*G128</f>
+      <c r="A128" t="s">
+        <v>30</v>
+      </c>
+      <c r="B128">
+        <f>SUM(B123:B125)</f>
       </c>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="H129">
-        <f>F129*G129</f>
-      </c>
-    </row>
-    <row r="130" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="H130">
-        <f>F130*G130</f>
-      </c>
-    </row>
-    <row r="131" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="H131">
-        <f>F131*G131</f>
-      </c>
-    </row>
-    <row r="132" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="H132">
-        <f>F132*G132</f>
-      </c>
-    </row>
-    <row r="133" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="H133">
-        <f>F133*G133</f>
-      </c>
-    </row>
-    <row r="134" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="H134">
-        <f>F134*G134</f>
-      </c>
-    </row>
-    <row r="135" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="H135">
-        <f>F135*G135</f>
-      </c>
-    </row>
-    <row r="136" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="H136">
-        <f>F136*G136</f>
-      </c>
-    </row>
-    <row r="137" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="H137">
-        <f>F137*G137</f>
-      </c>
-    </row>
-    <row r="138" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="H138">
-        <f>F138*G138</f>
-      </c>
-    </row>
-    <row r="139" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="H139">
-        <f>F139*G139</f>
-      </c>
-    </row>
-    <row r="140" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A140" t="s">
-        <v>29</v>
-      </c>
-      <c r="B140">
-        <f>SUM(H140:K140)</f>
-      </c>
-      <c r="H140">
-        <f>SUM(H121:H139)</f>
-      </c>
-      <c r="I140">
-        <f>SUM(I121:I139)</f>
-      </c>
-      <c r="K140">
-        <f>SUM(K121:K139)</f>
-      </c>
-    </row>
-    <row r="141" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A141" t="s">
-        <v>30</v>
-      </c>
-      <c r="B141">
-        <f>SUM(B122:B124)</f>
-      </c>
-    </row>
-    <row r="142" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A142" t="s">
+      <c r="A129" t="s">
         <v>31</v>
       </c>
-      <c r="B142">
-        <f>(B141-B140)/B141</f>
+      <c r="B129">
+        <f>(B128-B127)/B128</f>
       </c>
     </row>
   </sheetData>
@@ -1944,10 +1978,10 @@
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="C2" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="D2" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="E2" t="s">
         <v>13</v>
@@ -2190,7 +2224,7 @@
         <v>15</v>
       </c>
       <c r="D37" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="E37" t="s">
         <v>23</v>
@@ -2363,10 +2397,10 @@
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="C2" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="D2" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="E2" t="s">
         <v>13</v>
@@ -2384,7 +2418,7 @@
         <v>1200</v>
       </c>
       <c r="L2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="M2" t="s">
         <v>19</v>
@@ -2398,7 +2432,7 @@
         <v>19</v>
       </c>
       <c r="E3" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="F3">
         <v>24</v>
@@ -2575,21 +2609,21 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="F1" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="B2" t="s">
         <v>3</v>
       </c>
       <c r="C2" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -2605,12 +2639,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>
